--- a/results/01_pollution_assessment/MaxRel_Focus/tables/varpart_summary.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/varpart_summary.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1350928062507485</v>
+        <v>0.1073040241006735</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07567840890039612</v>
+        <v>0.1451463206249441</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1840894428698515</v>
+        <v>0.1932508701812915</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1084110339694554</v>
+        <v>0.04810454955634735</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02668177228129309</v>
+        <v>0.05919947454432617</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04899663661910303</v>
+        <v>0.08594684608061798</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8159105571301485</v>
+        <v>0.8067491298187085</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/MaxRel_Focus/tables/varpart_summary.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/varpart_summary.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1073040241006735</v>
+        <v>0.1232976611420695</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1451463206249441</v>
+        <v>0.121938119310435</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1932508701812915</v>
+        <v>0.1952777890250623</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04810454955634735</v>
+        <v>0.07333966971462735</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05919947454432617</v>
+        <v>0.04995799142744217</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08594684608061798</v>
+        <v>0.07198012788299279</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8067491298187085</v>
+        <v>0.8047222109749377</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/MaxRel_Focus/tables/varpart_summary.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/varpart_summary.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1232976611420695</v>
+        <v>0.2170673132792391</v>
       </c>
       <c r="C2" t="n">
-        <v>0.121938119310435</v>
+        <v>0.03673033551523686</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1952777890250623</v>
+        <v>0.2881840135170364</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07333966971462735</v>
+        <v>0.2514536780017995</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04995799142744217</v>
+        <v>-0.0343863647225604</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07198012788299279</v>
+        <v>0.07111670023779726</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8047222109749377</v>
+        <v>0.7118159864829636</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/MaxRel_Focus/tables/varpart_summary.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/varpart_summary.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2170673132792391</v>
+        <v>0.08084887391734308</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03673033551523686</v>
+        <v>0.06855592166176361</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2881840135170364</v>
+        <v>0.1392401692874681</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2514536780017995</v>
+        <v>0.07068424762570447</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0343863647225604</v>
+        <v>0.01016462629163861</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07111670023779726</v>
+        <v>0.058391295370125</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7118159864829636</v>
+        <v>0.8607598307125319</v>
       </c>
     </row>
   </sheetData>
